--- a/stella/test_fixtures/pantry_loaded/pos_data.xlsx
+++ b/stella/test_fixtures/pantry_loaded/pos_data.xlsx
@@ -499,10 +499,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2428.6</v>
+        <v>2420.68</v>
       </c>
       <c r="E2" t="n">
-        <v>388.6</v>
+        <v>387.3</v>
       </c>
       <c r="F2" t="n">
         <v>6.25</v>
@@ -535,10 +535,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2555.35</v>
+        <v>2517.53</v>
       </c>
       <c r="E3" t="n">
-        <v>408.9</v>
+        <v>402.8</v>
       </c>
       <c r="F3" t="n">
         <v>6.25</v>
@@ -571,10 +571,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2634.81</v>
+        <v>2628.85</v>
       </c>
       <c r="E4" t="n">
-        <v>439.1</v>
+        <v>438.1</v>
       </c>
       <c r="F4" t="n">
         <v>6</v>
@@ -601,10 +601,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2349.74</v>
+        <v>2352.37</v>
       </c>
       <c r="E5" t="n">
-        <v>361.5</v>
+        <v>361.9</v>
       </c>
       <c r="F5" t="n">
         <v>6.5</v>
@@ -631,10 +631,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2531.25</v>
+        <v>2516.21</v>
       </c>
       <c r="E6" t="n">
-        <v>405</v>
+        <v>402.6</v>
       </c>
       <c r="F6" t="n">
         <v>6.25</v>
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2407.23</v>
+        <v>2469.37</v>
       </c>
       <c r="E7" t="n">
-        <v>385.2</v>
+        <v>395.1</v>
       </c>
       <c r="F7" t="n">
         <v>6.25</v>
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2593.17</v>
+        <v>2719.64</v>
       </c>
       <c r="E8" t="n">
-        <v>432.2</v>
+        <v>453.3</v>
       </c>
       <c r="F8" t="n">
         <v>6</v>
@@ -733,10 +733,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2193.4</v>
+        <v>2188.15</v>
       </c>
       <c r="E9" t="n">
-        <v>337.4</v>
+        <v>336.6</v>
       </c>
       <c r="F9" t="n">
         <v>6.5</v>
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2521.19</v>
+        <v>2591.71</v>
       </c>
       <c r="E10" t="n">
-        <v>403.4</v>
+        <v>414.7</v>
       </c>
       <c r="F10" t="n">
         <v>6.25</v>
@@ -799,10 +799,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2560.3</v>
+        <v>2496.46</v>
       </c>
       <c r="E11" t="n">
-        <v>409.6</v>
+        <v>399.4</v>
       </c>
       <c r="F11" t="n">
         <v>6.25</v>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2643.53</v>
+        <v>2761.07</v>
       </c>
       <c r="E12" t="n">
-        <v>440.6</v>
+        <v>460.2</v>
       </c>
       <c r="F12" t="n">
         <v>6</v>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2338.59</v>
+        <v>2199.06</v>
       </c>
       <c r="E13" t="n">
-        <v>359.8</v>
+        <v>338.3</v>
       </c>
       <c r="F13" t="n">
         <v>6.5</v>
@@ -895,10 +895,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2411.45</v>
+        <v>2497.33</v>
       </c>
       <c r="E14" t="n">
-        <v>385.8</v>
+        <v>399.6</v>
       </c>
       <c r="F14" t="n">
         <v>6.25</v>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2560.19</v>
+        <v>2498.14</v>
       </c>
       <c r="E15" t="n">
-        <v>409.6</v>
+        <v>399.7</v>
       </c>
       <c r="F15" t="n">
         <v>6.25</v>
@@ -967,10 +967,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2792.4</v>
+        <v>2794.57</v>
       </c>
       <c r="E16" t="n">
-        <v>465.4</v>
+        <v>465.8</v>
       </c>
       <c r="F16" t="n">
         <v>6</v>
@@ -997,10 +997,10 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2324.52</v>
+        <v>2288.05</v>
       </c>
       <c r="E17" t="n">
-        <v>357.6</v>
+        <v>352</v>
       </c>
       <c r="F17" t="n">
         <v>6.5</v>
@@ -1027,16 +1027,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>4469.74</v>
+        <v>4390.67</v>
       </c>
       <c r="E18" t="n">
-        <v>893.9</v>
+        <v>878.1</v>
       </c>
       <c r="F18" t="n">
         <v>5</v>
       </c>
       <c r="G18" t="n">
-        <v>1117.43</v>
+        <v>1097.67</v>
       </c>
       <c r="H18" t="n">
         <v>0.65</v>
@@ -1063,16 +1063,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>4518.97</v>
+        <v>4317.98</v>
       </c>
       <c r="E19" t="n">
-        <v>903.8</v>
+        <v>863.6</v>
       </c>
       <c r="F19" t="n">
         <v>5</v>
       </c>
       <c r="G19" t="n">
-        <v>1129.74</v>
+        <v>1079.49</v>
       </c>
       <c r="H19" t="n">
         <v>0.65</v>
@@ -1099,10 +1099,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2548.66</v>
+        <v>2610.35</v>
       </c>
       <c r="E20" t="n">
-        <v>424.8</v>
+        <v>435.1</v>
       </c>
       <c r="F20" t="n">
         <v>6</v>
@@ -1129,10 +1129,10 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2176.31</v>
+        <v>2233.19</v>
       </c>
       <c r="E21" t="n">
-        <v>334.8</v>
+        <v>343.6</v>
       </c>
       <c r="F21" t="n">
         <v>6.5</v>
@@ -1159,16 +1159,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>4267.97</v>
+        <v>4378.5</v>
       </c>
       <c r="E22" t="n">
-        <v>853.6</v>
+        <v>875.7</v>
       </c>
       <c r="F22" t="n">
         <v>5</v>
       </c>
       <c r="G22" t="n">
-        <v>1066.99</v>
+        <v>1094.62</v>
       </c>
       <c r="H22" t="n">
         <v>0.65</v>
@@ -1195,16 +1195,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>4401.59</v>
+        <v>4231.61</v>
       </c>
       <c r="E23" t="n">
-        <v>880.3</v>
+        <v>846.3</v>
       </c>
       <c r="F23" t="n">
         <v>5</v>
       </c>
       <c r="G23" t="n">
-        <v>1100.4</v>
+        <v>1057.9</v>
       </c>
       <c r="H23" t="n">
         <v>0.65</v>
@@ -1231,10 +1231,10 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2697.9</v>
+        <v>2715.07</v>
       </c>
       <c r="E24" t="n">
-        <v>449.7</v>
+        <v>452.5</v>
       </c>
       <c r="F24" t="n">
         <v>6</v>
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2252.69</v>
+        <v>2300.16</v>
       </c>
       <c r="E25" t="n">
-        <v>346.6</v>
+        <v>353.9</v>
       </c>
       <c r="F25" t="n">
         <v>6.5</v>
@@ -1291,16 +1291,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>4523.6</v>
+        <v>4273.37</v>
       </c>
       <c r="E26" t="n">
-        <v>904.7</v>
+        <v>854.7</v>
       </c>
       <c r="F26" t="n">
         <v>5</v>
       </c>
       <c r="G26" t="n">
-        <v>1130.9</v>
+        <v>1068.34</v>
       </c>
       <c r="H26" t="n">
         <v>0.65</v>
@@ -1327,16 +1327,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>4278.63</v>
+        <v>4419.02</v>
       </c>
       <c r="E27" t="n">
-        <v>855.7</v>
+        <v>883.8</v>
       </c>
       <c r="F27" t="n">
         <v>5</v>
       </c>
       <c r="G27" t="n">
-        <v>1069.66</v>
+        <v>1104.76</v>
       </c>
       <c r="H27" t="n">
         <v>0.65</v>
@@ -1363,10 +1363,10 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2695.66</v>
+        <v>2563.14</v>
       </c>
       <c r="E28" t="n">
-        <v>449.3</v>
+        <v>427.2</v>
       </c>
       <c r="F28" t="n">
         <v>6</v>
@@ -1393,10 +1393,10 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2174.75</v>
+        <v>2260.22</v>
       </c>
       <c r="E29" t="n">
-        <v>334.6</v>
+        <v>347.7</v>
       </c>
       <c r="F29" t="n">
         <v>6.5</v>
@@ -1423,16 +1423,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>4319.31</v>
+        <v>4322.99</v>
       </c>
       <c r="E30" t="n">
-        <v>863.9</v>
+        <v>864.6</v>
       </c>
       <c r="F30" t="n">
         <v>5</v>
       </c>
       <c r="G30" t="n">
-        <v>1079.83</v>
+        <v>1080.75</v>
       </c>
       <c r="H30" t="n">
         <v>0.65</v>
@@ -1459,16 +1459,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>4473.89</v>
+        <v>4456.12</v>
       </c>
       <c r="E31" t="n">
-        <v>894.8</v>
+        <v>891.2</v>
       </c>
       <c r="F31" t="n">
         <v>5</v>
       </c>
       <c r="G31" t="n">
-        <v>1118.47</v>
+        <v>1114.03</v>
       </c>
       <c r="H31" t="n">
         <v>0.65</v>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2747.65</v>
+        <v>2694.05</v>
       </c>
       <c r="E32" t="n">
-        <v>457.9</v>
+        <v>449</v>
       </c>
       <c r="F32" t="n">
         <v>6</v>
@@ -1525,10 +1525,10 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2249.39</v>
+        <v>2277.42</v>
       </c>
       <c r="E33" t="n">
-        <v>346.1</v>
+        <v>350.4</v>
       </c>
       <c r="F33" t="n">
         <v>6.5</v>
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1639.41</v>
+        <v>1646.65</v>
       </c>
       <c r="E34" t="n">
-        <v>262.3</v>
+        <v>263.5</v>
       </c>
       <c r="F34" t="n">
         <v>6.25</v>
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1715.82</v>
+        <v>1756.58</v>
       </c>
       <c r="E35" t="n">
-        <v>274.5</v>
+        <v>281.1</v>
       </c>
       <c r="F35" t="n">
         <v>6.25</v>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2601.15</v>
+        <v>2641.73</v>
       </c>
       <c r="E36" t="n">
-        <v>433.5</v>
+        <v>440.3</v>
       </c>
       <c r="F36" t="n">
         <v>6</v>
@@ -1657,10 +1657,10 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2344.91</v>
+        <v>2190.81</v>
       </c>
       <c r="E37" t="n">
-        <v>360.8</v>
+        <v>337</v>
       </c>
       <c r="F37" t="n">
         <v>6.5</v>
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1728.5</v>
+        <v>1707.46</v>
       </c>
       <c r="E38" t="n">
-        <v>276.6</v>
+        <v>273.2</v>
       </c>
       <c r="F38" t="n">
         <v>6.25</v>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1655.55</v>
+        <v>1682.45</v>
       </c>
       <c r="E39" t="n">
-        <v>264.9</v>
+        <v>269.2</v>
       </c>
       <c r="F39" t="n">
         <v>6.25</v>
@@ -1759,10 +1759,10 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2611.81</v>
+        <v>2771.23</v>
       </c>
       <c r="E40" t="n">
-        <v>435.3</v>
+        <v>461.9</v>
       </c>
       <c r="F40" t="n">
         <v>6</v>
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2217.4</v>
+        <v>2331.1</v>
       </c>
       <c r="E41" t="n">
-        <v>341.1</v>
+        <v>358.6</v>
       </c>
       <c r="F41" t="n">
         <v>6.5</v>
@@ -1819,10 +1819,10 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1765.28</v>
+        <v>1675.13</v>
       </c>
       <c r="E42" t="n">
-        <v>282.4</v>
+        <v>268</v>
       </c>
       <c r="F42" t="n">
         <v>6.25</v>
@@ -1855,10 +1855,10 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1694.36</v>
+        <v>1761.59</v>
       </c>
       <c r="E43" t="n">
-        <v>271.1</v>
+        <v>281.9</v>
       </c>
       <c r="F43" t="n">
         <v>6.25</v>
@@ -1891,10 +1891,10 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2761.36</v>
+        <v>2654.84</v>
       </c>
       <c r="E44" t="n">
-        <v>460.2</v>
+        <v>442.5</v>
       </c>
       <c r="F44" t="n">
         <v>6</v>
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2299.83</v>
+        <v>2277.74</v>
       </c>
       <c r="E45" t="n">
-        <v>353.8</v>
+        <v>350.4</v>
       </c>
       <c r="F45" t="n">
         <v>6.5</v>
@@ -1951,10 +1951,10 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1709.85</v>
+        <v>1666.81</v>
       </c>
       <c r="E46" t="n">
-        <v>273.6</v>
+        <v>266.7</v>
       </c>
       <c r="F46" t="n">
         <v>6.25</v>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1651.74</v>
+        <v>1759.3</v>
       </c>
       <c r="E47" t="n">
-        <v>264.3</v>
+        <v>281.5</v>
       </c>
       <c r="F47" t="n">
         <v>6.25</v>
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>2796.34</v>
+        <v>2627.56</v>
       </c>
       <c r="E48" t="n">
-        <v>466.1</v>
+        <v>437.9</v>
       </c>
       <c r="F48" t="n">
         <v>6</v>
@@ -2053,10 +2053,10 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2238.84</v>
+        <v>2192.17</v>
       </c>
       <c r="E49" t="n">
-        <v>344.4</v>
+        <v>337.3</v>
       </c>
       <c r="F49" t="n">
         <v>6.5</v>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2012.48</v>
+        <v>1989.62</v>
       </c>
       <c r="E50" t="n">
-        <v>322</v>
+        <v>318.3</v>
       </c>
       <c r="F50" t="n">
         <v>6.25</v>
@@ -2119,10 +2119,10 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2031.96</v>
+        <v>2078.78</v>
       </c>
       <c r="E51" t="n">
-        <v>325.1</v>
+        <v>332.6</v>
       </c>
       <c r="F51" t="n">
         <v>6.25</v>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>2732.23</v>
+        <v>2784.6</v>
       </c>
       <c r="E52" t="n">
-        <v>455.4</v>
+        <v>464.1</v>
       </c>
       <c r="F52" t="n">
         <v>6</v>
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>2355.19</v>
+        <v>2320.25</v>
       </c>
       <c r="E53" t="n">
-        <v>362.3</v>
+        <v>357</v>
       </c>
       <c r="F53" t="n">
         <v>6.5</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1943.75</v>
+        <v>2062.53</v>
       </c>
       <c r="E54" t="n">
-        <v>311</v>
+        <v>330</v>
       </c>
       <c r="F54" t="n">
         <v>6.25</v>
@@ -2251,10 +2251,10 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>2001.34</v>
+        <v>2062.95</v>
       </c>
       <c r="E55" t="n">
-        <v>320.2</v>
+        <v>330.1</v>
       </c>
       <c r="F55" t="n">
         <v>6.25</v>
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>2679.27</v>
+        <v>2704.07</v>
       </c>
       <c r="E56" t="n">
-        <v>446.5</v>
+        <v>450.7</v>
       </c>
       <c r="F56" t="n">
         <v>6</v>
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>2270.3</v>
+        <v>2241.5</v>
       </c>
       <c r="E57" t="n">
-        <v>349.3</v>
+        <v>344.8</v>
       </c>
       <c r="F57" t="n">
         <v>6.5</v>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>2181.46</v>
+        <v>2298.96</v>
       </c>
       <c r="E58" t="n">
-        <v>349</v>
+        <v>367.8</v>
       </c>
       <c r="F58" t="n">
         <v>6.25</v>
@@ -2383,10 +2383,10 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>2184.14</v>
+        <v>2279.1</v>
       </c>
       <c r="E59" t="n">
-        <v>349.5</v>
+        <v>364.7</v>
       </c>
       <c r="F59" t="n">
         <v>6.25</v>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>2652.06</v>
+        <v>2672.71</v>
       </c>
       <c r="E60" t="n">
-        <v>442</v>
+        <v>445.5</v>
       </c>
       <c r="F60" t="n">
         <v>6</v>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>2239.46</v>
+        <v>2201.19</v>
       </c>
       <c r="E61" t="n">
-        <v>344.5</v>
+        <v>338.6</v>
       </c>
       <c r="F61" t="n">
         <v>6.5</v>
@@ -2479,10 +2479,10 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>2237.02</v>
+        <v>2294.42</v>
       </c>
       <c r="E62" t="n">
-        <v>357.9</v>
+        <v>367.1</v>
       </c>
       <c r="F62" t="n">
         <v>6.25</v>
@@ -2515,10 +2515,10 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>2269.98</v>
+        <v>2207.24</v>
       </c>
       <c r="E63" t="n">
-        <v>363.2</v>
+        <v>353.2</v>
       </c>
       <c r="F63" t="n">
         <v>6.25</v>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>2729.08</v>
+        <v>2794.35</v>
       </c>
       <c r="E64" t="n">
-        <v>454.8</v>
+        <v>465.7</v>
       </c>
       <c r="F64" t="n">
         <v>6</v>
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>2258.95</v>
+        <v>2227.86</v>
       </c>
       <c r="E65" t="n">
-        <v>347.5</v>
+        <v>342.7</v>
       </c>
       <c r="F65" t="n">
         <v>6.5</v>

--- a/stella/test_fixtures/pantry_loaded/pos_data.xlsx
+++ b/stella/test_fixtures/pantry_loaded/pos_data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J65"/>
+  <dimension ref="A1:J241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,29 +495,29 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SF-Whitening 6oz</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2420.68</v>
+        <v>3266.31</v>
       </c>
       <c r="E2" t="n">
-        <v>387.3</v>
+        <v>519.3</v>
       </c>
       <c r="F2" t="n">
-        <v>6.25</v>
+        <v>6.29</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.55</v>
+        <v>0.7</v>
       </c>
       <c r="I2" t="n">
-        <v>0.28</v>
+        <v>0.18</v>
       </c>
       <c r="J2" t="n">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="3">
@@ -531,29 +531,29 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SF-Sensitivity 4oz</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2517.53</v>
+        <v>3171.97</v>
       </c>
       <c r="E3" t="n">
-        <v>402.8</v>
+        <v>504.3</v>
       </c>
       <c r="F3" t="n">
-        <v>6.25</v>
+        <v>6.29</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.55</v>
+        <v>0.7</v>
       </c>
       <c r="I3" t="n">
-        <v>0.28</v>
+        <v>0.18</v>
       </c>
       <c r="J3" t="n">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="4">
@@ -562,29 +562,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>Summit Foods</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>SF-Complete 6oz</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2628.85</v>
+        <v>3126.12</v>
       </c>
       <c r="E4" t="n">
-        <v>438.1</v>
+        <v>497</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>6.29</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.12</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -592,22 +598,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>PearlCare</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>PC-Deep Clean 6oz</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2352.37</v>
+        <v>2890.12</v>
       </c>
       <c r="E5" t="n">
-        <v>361.9</v>
+        <v>445.3</v>
       </c>
       <c r="F5" t="n">
-        <v>6.5</v>
+        <v>6.49</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -618,98 +624,86 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45668</v>
+        <v>45661</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>PearlCare</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>PC-Gentle 4oz</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2516.21</v>
+        <v>2901.25</v>
       </c>
       <c r="E6" t="n">
-        <v>402.6</v>
+        <v>447</v>
       </c>
       <c r="F6" t="n">
-        <v>6.25</v>
+        <v>6.49</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.17</v>
-      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45668</v>
+        <v>45661</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>PearlCare</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>PC-Total 6oz</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2469.37</v>
+        <v>2831.34</v>
       </c>
       <c r="E7" t="n">
-        <v>395.1</v>
+        <v>436.3</v>
       </c>
       <c r="F7" t="n">
-        <v>6.25</v>
+        <v>6.49</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.17</v>
-      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45668</v>
+        <v>45661</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>CleanPro</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>CP-Fresh 6oz</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2719.64</v>
+        <v>3073.81</v>
       </c>
       <c r="E8" t="n">
-        <v>453.3</v>
+        <v>716.5</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>4.29</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -720,26 +714,26 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45668</v>
+        <v>45661</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>CleanPro</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>CP-Cavity Shield 4oz</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2188.15</v>
+        <v>3084.13</v>
       </c>
       <c r="E9" t="n">
-        <v>336.6</v>
+        <v>718.9</v>
       </c>
       <c r="F9" t="n">
-        <v>6.5</v>
+        <v>4.29</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -750,98 +744,86 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45675</v>
+        <v>45661</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>CleanPro</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>CP-Mint Blast 6oz</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2591.71</v>
+        <v>2951.2</v>
       </c>
       <c r="E10" t="n">
-        <v>414.7</v>
+        <v>687.9</v>
       </c>
       <c r="F10" t="n">
-        <v>6.25</v>
+        <v>4.29</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.17</v>
-      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45675</v>
+        <v>45661</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>DailyShine</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>DS-Original 6oz</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2496.46</v>
+        <v>2616.77</v>
       </c>
       <c r="E11" t="n">
-        <v>399.4</v>
+        <v>639.8</v>
       </c>
       <c r="F11" t="n">
-        <v>6.25</v>
+        <v>4.09</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
-      <c r="H11" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.17</v>
-      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45675</v>
+        <v>45661</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>DailyShine</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>DS-Whitening 4oz</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2761.07</v>
+        <v>2738.11</v>
       </c>
       <c r="E12" t="n">
-        <v>460.2</v>
+        <v>669.5</v>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>4.09</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -852,26 +834,26 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45675</v>
+        <v>45661</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>DailyShine</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>DS-Cool Mint 6oz</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2199.06</v>
+        <v>2557.26</v>
       </c>
       <c r="E13" t="n">
-        <v>338.3</v>
+        <v>625.2</v>
       </c>
       <c r="F13" t="n">
-        <v>6.5</v>
+        <v>4.09</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -882,98 +864,86 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45682</v>
+        <v>45661</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>SmartChoice</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SC-Basic Clean 6oz</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2497.33</v>
+        <v>2235.65</v>
       </c>
       <c r="E14" t="n">
-        <v>399.6</v>
+        <v>801.3</v>
       </c>
       <c r="F14" t="n">
-        <v>6.25</v>
+        <v>2.79</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
-      <c r="H14" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.17</v>
-      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45682</v>
+        <v>45661</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>SmartChoice</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SC-Whitening 4oz</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2498.14</v>
+        <v>2225.51</v>
       </c>
       <c r="E15" t="n">
-        <v>399.7</v>
+        <v>797.7</v>
       </c>
       <c r="F15" t="n">
-        <v>6.25</v>
+        <v>2.79</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
-      <c r="H15" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.17</v>
-      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45682</v>
+        <v>45661</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>SmartChoice</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>SC-Fresh 6oz</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2794.57</v>
+        <v>2265.95</v>
       </c>
       <c r="E16" t="n">
-        <v>465.8</v>
+        <v>812.2</v>
       </c>
       <c r="F16" t="n">
-        <v>6</v>
+        <v>2.79</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -984,37 +954,43 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45682</v>
+        <v>45668</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>Summit Foods</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>SF-Whitening 6oz</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2288.05</v>
+        <v>3060.31</v>
       </c>
       <c r="E17" t="n">
-        <v>352</v>
+        <v>486.5</v>
       </c>
       <c r="F17" t="n">
-        <v>6.5</v>
+        <v>6.29</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.12</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45689</v>
+        <v>45668</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1023,34 +999,34 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SF-Sensitivity 4oz</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>4390.67</v>
+        <v>3187.35</v>
       </c>
       <c r="E18" t="n">
-        <v>878.1</v>
+        <v>506.7</v>
       </c>
       <c r="F18" t="n">
-        <v>5</v>
+        <v>6.29</v>
       </c>
       <c r="G18" t="n">
-        <v>1097.67</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="I18" t="n">
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="J18" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45689</v>
+        <v>45668</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1059,53 +1035,53 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SF-Complete 6oz</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>4317.98</v>
+        <v>3113.99</v>
       </c>
       <c r="E19" t="n">
-        <v>863.6</v>
+        <v>495.1</v>
       </c>
       <c r="F19" t="n">
-        <v>5</v>
+        <v>6.29</v>
       </c>
       <c r="G19" t="n">
-        <v>1079.49</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="I19" t="n">
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="J19" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45689</v>
+        <v>45668</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>PearlCare</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>PC-Deep Clean 6oz</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2610.35</v>
+        <v>2948.24</v>
       </c>
       <c r="E20" t="n">
-        <v>435.1</v>
+        <v>454.3</v>
       </c>
       <c r="F20" t="n">
-        <v>6</v>
+        <v>6.49</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1116,26 +1092,26 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45689</v>
+        <v>45668</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>PearlCare</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>PC-Gentle 4oz</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2233.19</v>
+        <v>2813.05</v>
       </c>
       <c r="E21" t="n">
-        <v>343.6</v>
+        <v>433.4</v>
       </c>
       <c r="F21" t="n">
-        <v>6.5</v>
+        <v>6.49</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1146,98 +1122,86 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45696</v>
+        <v>45668</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>PearlCare</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>PC-Total 6oz</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>4378.5</v>
+        <v>2911.56</v>
       </c>
       <c r="E22" t="n">
-        <v>875.7</v>
+        <v>448.6</v>
       </c>
       <c r="F22" t="n">
-        <v>5</v>
+        <v>6.49</v>
       </c>
       <c r="G22" t="n">
-        <v>1094.62</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.13</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45696</v>
+        <v>45668</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>CleanPro</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>CP-Fresh 6oz</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>4231.61</v>
+        <v>3008.35</v>
       </c>
       <c r="E23" t="n">
-        <v>846.3</v>
+        <v>701.2</v>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>4.29</v>
       </c>
       <c r="G23" t="n">
-        <v>1057.9</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.13</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45696</v>
+        <v>45668</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>CleanPro</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>CP-Cavity Shield 4oz</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2715.07</v>
+        <v>2934.37</v>
       </c>
       <c r="E24" t="n">
-        <v>452.5</v>
+        <v>684</v>
       </c>
       <c r="F24" t="n">
-        <v>6</v>
+        <v>4.29</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1248,26 +1212,26 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45696</v>
+        <v>45668</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>CleanPro</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>CP-Mint Blast 6oz</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2300.16</v>
+        <v>2916.42</v>
       </c>
       <c r="E25" t="n">
-        <v>353.9</v>
+        <v>679.8</v>
       </c>
       <c r="F25" t="n">
-        <v>6.5</v>
+        <v>4.29</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1278,98 +1242,86 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45703</v>
+        <v>45668</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>DailyShine</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>DS-Original 6oz</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>4273.37</v>
+        <v>2592.24</v>
       </c>
       <c r="E26" t="n">
-        <v>854.7</v>
+        <v>633.8</v>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>4.09</v>
       </c>
       <c r="G26" t="n">
-        <v>1068.34</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.13</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45703</v>
+        <v>45668</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>DailyShine</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>DS-Whitening 4oz</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>4419.02</v>
+        <v>2625.35</v>
       </c>
       <c r="E27" t="n">
-        <v>883.8</v>
+        <v>641.9</v>
       </c>
       <c r="F27" t="n">
-        <v>5</v>
+        <v>4.09</v>
       </c>
       <c r="G27" t="n">
-        <v>1104.76</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.13</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45703</v>
+        <v>45668</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>DailyShine</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>DS-Cool Mint 6oz</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2563.14</v>
+        <v>2572.75</v>
       </c>
       <c r="E28" t="n">
-        <v>427.2</v>
+        <v>629</v>
       </c>
       <c r="F28" t="n">
-        <v>6</v>
+        <v>4.09</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1380,26 +1332,26 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45703</v>
+        <v>45668</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>SmartChoice</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>SC-Basic Clean 6oz</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2260.22</v>
+        <v>2311.87</v>
       </c>
       <c r="E29" t="n">
-        <v>347.7</v>
+        <v>828.6</v>
       </c>
       <c r="F29" t="n">
-        <v>6.5</v>
+        <v>2.79</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1410,139 +1362,139 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45710</v>
+        <v>45668</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>SmartChoice</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SC-Whitening 4oz</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>4322.99</v>
+        <v>2215.04</v>
       </c>
       <c r="E30" t="n">
-        <v>864.6</v>
+        <v>793.9</v>
       </c>
       <c r="F30" t="n">
-        <v>5</v>
+        <v>2.79</v>
       </c>
       <c r="G30" t="n">
-        <v>1080.75</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.13</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45710</v>
+        <v>45668</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>SmartChoice</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SC-Fresh 6oz</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>4456.12</v>
+        <v>2287.17</v>
       </c>
       <c r="E31" t="n">
-        <v>891.2</v>
+        <v>819.8</v>
       </c>
       <c r="F31" t="n">
-        <v>5</v>
+        <v>2.79</v>
       </c>
       <c r="G31" t="n">
-        <v>1114.03</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0.13</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45710</v>
+        <v>45675</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>Summit Foods</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>SF-Whitening 6oz</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2694.05</v>
+        <v>3264.36</v>
       </c>
       <c r="E32" t="n">
-        <v>449</v>
+        <v>519</v>
       </c>
       <c r="F32" t="n">
-        <v>6</v>
+        <v>6.29</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+      <c r="H32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.12</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45710</v>
+        <v>45675</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>Summit Foods</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>SF-Sensitivity 4oz</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2277.42</v>
+        <v>3039.51</v>
       </c>
       <c r="E33" t="n">
-        <v>350.4</v>
+        <v>483.2</v>
       </c>
       <c r="F33" t="n">
-        <v>6.5</v>
+        <v>6.29</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+      <c r="H33" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.12</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45717</v>
+        <v>45675</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1551,89 +1503,83 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SF-Complete 6oz</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1646.65</v>
+        <v>3183.16</v>
       </c>
       <c r="E34" t="n">
-        <v>263.5</v>
+        <v>506.1</v>
       </c>
       <c r="F34" t="n">
-        <v>6.25</v>
+        <v>6.29</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="I34" t="n">
-        <v>0.24</v>
+        <v>0.18</v>
       </c>
       <c r="J34" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45717</v>
+        <v>45675</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>PearlCare</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>PC-Deep Clean 6oz</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1756.58</v>
+        <v>3007.28</v>
       </c>
       <c r="E35" t="n">
-        <v>281.1</v>
+        <v>463.4</v>
       </c>
       <c r="F35" t="n">
-        <v>6.25</v>
+        <v>6.49</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
-      <c r="H35" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0.16</v>
-      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45717</v>
+        <v>45675</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>PearlCare</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>PC-Gentle 4oz</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2641.73</v>
+        <v>2951.86</v>
       </c>
       <c r="E36" t="n">
-        <v>440.3</v>
+        <v>454.8</v>
       </c>
       <c r="F36" t="n">
-        <v>6</v>
+        <v>6.49</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1644,26 +1590,26 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45717</v>
+        <v>45675</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>PearlCare</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>PC-Total 6oz</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2190.81</v>
+        <v>2903.92</v>
       </c>
       <c r="E37" t="n">
-        <v>337</v>
+        <v>447.4</v>
       </c>
       <c r="F37" t="n">
-        <v>6.5</v>
+        <v>6.49</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1674,98 +1620,86 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45724</v>
+        <v>45675</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>CleanPro</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>CP-Fresh 6oz</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1707.46</v>
+        <v>2986.44</v>
       </c>
       <c r="E38" t="n">
-        <v>273.2</v>
+        <v>696.1</v>
       </c>
       <c r="F38" t="n">
-        <v>6.25</v>
+        <v>4.29</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
-      <c r="H38" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0.16</v>
-      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45724</v>
+        <v>45675</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>CleanPro</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>CP-Cavity Shield 4oz</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1682.45</v>
+        <v>2891.5</v>
       </c>
       <c r="E39" t="n">
-        <v>269.2</v>
+        <v>674</v>
       </c>
       <c r="F39" t="n">
-        <v>6.25</v>
+        <v>4.29</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
-      <c r="H39" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0.16</v>
-      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45724</v>
+        <v>45675</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>CleanPro</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>CP-Mint Blast 6oz</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2771.23</v>
+        <v>3011.31</v>
       </c>
       <c r="E40" t="n">
-        <v>461.9</v>
+        <v>701.9</v>
       </c>
       <c r="F40" t="n">
-        <v>6</v>
+        <v>4.29</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1776,26 +1710,26 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45724</v>
+        <v>45675</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>DailyShine</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>DS-Original 6oz</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2331.1</v>
+        <v>2763.47</v>
       </c>
       <c r="E41" t="n">
-        <v>358.6</v>
+        <v>675.7</v>
       </c>
       <c r="F41" t="n">
-        <v>6.5</v>
+        <v>4.09</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1806,98 +1740,86 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45731</v>
+        <v>45675</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>DailyShine</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>DS-Whitening 4oz</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1675.13</v>
+        <v>2756.06</v>
       </c>
       <c r="E42" t="n">
-        <v>268</v>
+        <v>673.9</v>
       </c>
       <c r="F42" t="n">
-        <v>6.25</v>
+        <v>4.09</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
-      <c r="H42" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0.16</v>
-      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45731</v>
+        <v>45675</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>DailyShine</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>DS-Cool Mint 6oz</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1761.59</v>
+        <v>2560.75</v>
       </c>
       <c r="E43" t="n">
-        <v>281.9</v>
+        <v>626.1</v>
       </c>
       <c r="F43" t="n">
-        <v>6.25</v>
+        <v>4.09</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
-      <c r="H43" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0.16</v>
-      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45731</v>
+        <v>45675</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>SmartChoice</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>SC-Basic Clean 6oz</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2654.84</v>
+        <v>2268.75</v>
       </c>
       <c r="E44" t="n">
-        <v>442.5</v>
+        <v>813.2</v>
       </c>
       <c r="F44" t="n">
-        <v>6</v>
+        <v>2.79</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1908,26 +1830,26 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45731</v>
+        <v>45675</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>SmartChoice</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>SC-Whitening 4oz</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2277.74</v>
+        <v>2196.6</v>
       </c>
       <c r="E45" t="n">
-        <v>350.4</v>
+        <v>787.3</v>
       </c>
       <c r="F45" t="n">
-        <v>6.5</v>
+        <v>2.79</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1938,43 +1860,37 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45738</v>
+        <v>45675</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>SmartChoice</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SC-Fresh 6oz</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1666.81</v>
+        <v>2303.96</v>
       </c>
       <c r="E46" t="n">
-        <v>266.7</v>
+        <v>825.8</v>
       </c>
       <c r="F46" t="n">
-        <v>6.25</v>
+        <v>2.79</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
-      <c r="H46" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0.16</v>
-      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45738</v>
+        <v>45682</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -1983,185 +1899,185 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SF-Whitening 6oz</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1759.3</v>
+        <v>3030.55</v>
       </c>
       <c r="E47" t="n">
-        <v>281.5</v>
+        <v>481.8</v>
       </c>
       <c r="F47" t="n">
-        <v>6.25</v>
+        <v>6.29</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="I47" t="n">
-        <v>0.24</v>
+        <v>0.18</v>
       </c>
       <c r="J47" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45738</v>
+        <v>45682</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>Summit Foods</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>SF-Sensitivity 4oz</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>2627.56</v>
+        <v>3254.67</v>
       </c>
       <c r="E48" t="n">
-        <v>437.9</v>
+        <v>517.4</v>
       </c>
       <c r="F48" t="n">
-        <v>6</v>
+        <v>6.29</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+      <c r="H48" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.12</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45738</v>
+        <v>45682</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>Summit Foods</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>SF-Complete 6oz</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2192.17</v>
+        <v>3229.91</v>
       </c>
       <c r="E49" t="n">
-        <v>337.3</v>
+        <v>513.5</v>
       </c>
       <c r="F49" t="n">
-        <v>6.5</v>
+        <v>6.29</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+      <c r="H49" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.12</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45745</v>
+        <v>45682</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>PearlCare</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>PC-Deep Clean 6oz</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1989.62</v>
+        <v>2831.13</v>
       </c>
       <c r="E50" t="n">
-        <v>318.3</v>
+        <v>436.2</v>
       </c>
       <c r="F50" t="n">
-        <v>6.25</v>
+        <v>6.49</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
-      <c r="H50" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0.17</v>
-      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45745</v>
+        <v>45682</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>PearlCare</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>PC-Gentle 4oz</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2078.78</v>
+        <v>2817.66</v>
       </c>
       <c r="E51" t="n">
-        <v>332.6</v>
+        <v>434.2</v>
       </c>
       <c r="F51" t="n">
-        <v>6.25</v>
+        <v>6.49</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
-      <c r="H51" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0.17</v>
-      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45745</v>
+        <v>45682</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>PearlCare</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>PC-Total 6oz</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>2784.6</v>
+        <v>2998.7</v>
       </c>
       <c r="E52" t="n">
-        <v>464.1</v>
+        <v>462</v>
       </c>
       <c r="F52" t="n">
-        <v>6</v>
+        <v>6.49</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -2172,26 +2088,26 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>45745</v>
+        <v>45682</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>CleanPro</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>CP-Fresh 6oz</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>2320.25</v>
+        <v>2920.3</v>
       </c>
       <c r="E53" t="n">
-        <v>357</v>
+        <v>680.7</v>
       </c>
       <c r="F53" t="n">
-        <v>6.5</v>
+        <v>4.29</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -2202,98 +2118,86 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>45752</v>
+        <v>45682</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>CleanPro</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>CP-Cavity Shield 4oz</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2062.53</v>
+        <v>3011.38</v>
       </c>
       <c r="E54" t="n">
-        <v>330</v>
+        <v>702</v>
       </c>
       <c r="F54" t="n">
-        <v>6.25</v>
+        <v>4.29</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
-      <c r="H54" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0.17</v>
-      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>45752</v>
+        <v>45682</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>CleanPro</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>CP-Mint Blast 6oz</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>2062.95</v>
+        <v>3102.88</v>
       </c>
       <c r="E55" t="n">
-        <v>330.1</v>
+        <v>723.3</v>
       </c>
       <c r="F55" t="n">
-        <v>6.25</v>
+        <v>4.29</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
-      <c r="H55" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0.17</v>
-      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>45752</v>
+        <v>45682</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>DailyShine</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>DS-Original 6oz</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>2704.07</v>
+        <v>2672.84</v>
       </c>
       <c r="E56" t="n">
-        <v>450.7</v>
+        <v>653.5</v>
       </c>
       <c r="F56" t="n">
-        <v>6</v>
+        <v>4.09</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -2304,26 +2208,26 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>45752</v>
+        <v>45682</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>DailyShine</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>DS-Whitening 4oz</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>2241.5</v>
+        <v>2636.64</v>
       </c>
       <c r="E57" t="n">
-        <v>344.8</v>
+        <v>644.7</v>
       </c>
       <c r="F57" t="n">
-        <v>6.5</v>
+        <v>4.09</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -2334,98 +2238,86 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>45759</v>
+        <v>45682</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>DailyShine</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>DS-Cool Mint 6oz</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>2298.96</v>
+        <v>2646.81</v>
       </c>
       <c r="E58" t="n">
-        <v>367.8</v>
+        <v>647.1</v>
       </c>
       <c r="F58" t="n">
-        <v>6.25</v>
+        <v>4.09</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
-      <c r="H58" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="I58" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="J58" t="n">
-        <v>0.17</v>
-      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>45759</v>
+        <v>45682</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Summit Foods</t>
+          <t>SmartChoice</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SC-Basic Clean 6oz</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>2279.1</v>
+        <v>2153.99</v>
       </c>
       <c r="E59" t="n">
-        <v>364.7</v>
+        <v>772</v>
       </c>
       <c r="F59" t="n">
-        <v>6.25</v>
+        <v>2.79</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
-      <c r="H59" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="I59" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="J59" t="n">
-        <v>0.17</v>
-      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>45759</v>
+        <v>45682</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>SmartChoice</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>SC-Whitening 4oz</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>2672.71</v>
+        <v>2315.7</v>
       </c>
       <c r="E60" t="n">
-        <v>445.5</v>
+        <v>830</v>
       </c>
       <c r="F60" t="n">
-        <v>6</v>
+        <v>2.79</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2436,26 +2328,26 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>45759</v>
+        <v>45682</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>SmartChoice</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>SC-Fresh 6oz</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>2201.19</v>
+        <v>2198.19</v>
       </c>
       <c r="E61" t="n">
-        <v>338.6</v>
+        <v>787.9</v>
       </c>
       <c r="F61" t="n">
-        <v>6.5</v>
+        <v>2.79</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2466,7 +2358,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>45766</v>
+        <v>45689</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -2475,34 +2367,34 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SF-Whitening 6oz</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>2294.42</v>
+        <v>5406.23</v>
       </c>
       <c r="E62" t="n">
-        <v>367.1</v>
+        <v>1072.7</v>
       </c>
       <c r="F62" t="n">
-        <v>6.25</v>
+        <v>5.04</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>1340.83</v>
       </c>
       <c r="H62" t="n">
-        <v>0.58</v>
+        <v>0.65</v>
       </c>
       <c r="I62" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="J62" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>45766</v>
+        <v>45689</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -2511,83 +2403,89 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SF-Sensitivity 4oz</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>2207.24</v>
+        <v>5449.11</v>
       </c>
       <c r="E63" t="n">
-        <v>353.2</v>
+        <v>1081.2</v>
       </c>
       <c r="F63" t="n">
-        <v>6.25</v>
+        <v>5.04</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>1351.47</v>
       </c>
       <c r="H63" t="n">
-        <v>0.58</v>
+        <v>0.65</v>
       </c>
       <c r="I63" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="J63" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>45766</v>
+        <v>45689</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>RiverBrand</t>
+          <t>Summit Foods</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>RB-Classic 12ct</t>
+          <t>SF-Complete 6oz</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>2794.35</v>
+        <v>5749.96</v>
       </c>
       <c r="E64" t="n">
-        <v>465.7</v>
+        <v>1140.9</v>
       </c>
       <c r="F64" t="n">
-        <v>6</v>
+        <v>5.04</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+        <v>1426.08</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0.13</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>45766</v>
+        <v>45689</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CrestLine</t>
+          <t>PearlCare</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>CL-Premium 12ct</t>
+          <t>PC-Deep Clean 6oz</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>2227.86</v>
+        <v>2684.42</v>
       </c>
       <c r="E65" t="n">
-        <v>342.7</v>
+        <v>413.6</v>
       </c>
       <c r="F65" t="n">
-        <v>6.5</v>
+        <v>6.49</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2595,6 +2493,5484 @@
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>PC-Gentle 4oz</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>2856</v>
+      </c>
+      <c r="E66" t="n">
+        <v>440.1</v>
+      </c>
+      <c r="F66" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>PC-Total 6oz</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>2820.61</v>
+      </c>
+      <c r="E67" t="n">
+        <v>434.6</v>
+      </c>
+      <c r="F67" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>CP-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>3020.64</v>
+      </c>
+      <c r="E68" t="n">
+        <v>704.1</v>
+      </c>
+      <c r="F68" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>CP-Cavity Shield 4oz</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>3054.98</v>
+      </c>
+      <c r="E69" t="n">
+        <v>712.1</v>
+      </c>
+      <c r="F69" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>CP-Mint Blast 6oz</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>3023.5</v>
+      </c>
+      <c r="E70" t="n">
+        <v>704.8</v>
+      </c>
+      <c r="F70" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>DS-Original 6oz</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>2697.74</v>
+      </c>
+      <c r="E71" t="n">
+        <v>659.6</v>
+      </c>
+      <c r="F71" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>DS-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>2527.57</v>
+      </c>
+      <c r="E72" t="n">
+        <v>618</v>
+      </c>
+      <c r="F72" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>DS-Cool Mint 6oz</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>2666.98</v>
+      </c>
+      <c r="E73" t="n">
+        <v>652.1</v>
+      </c>
+      <c r="F73" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>SC-Basic Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>2240.16</v>
+      </c>
+      <c r="E74" t="n">
+        <v>802.9</v>
+      </c>
+      <c r="F74" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>SC-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>2239.77</v>
+      </c>
+      <c r="E75" t="n">
+        <v>802.8</v>
+      </c>
+      <c r="F75" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>SC-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>2303.23</v>
+      </c>
+      <c r="E76" t="n">
+        <v>825.5</v>
+      </c>
+      <c r="F76" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>5753.25</v>
+      </c>
+      <c r="E77" t="n">
+        <v>1141.5</v>
+      </c>
+      <c r="F77" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="G77" t="n">
+        <v>1426.9</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>5634.85</v>
+      </c>
+      <c r="E78" t="n">
+        <v>1118</v>
+      </c>
+      <c r="F78" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="G78" t="n">
+        <v>1397.53</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>5536.43</v>
+      </c>
+      <c r="E79" t="n">
+        <v>1098.5</v>
+      </c>
+      <c r="F79" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="G79" t="n">
+        <v>1373.12</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>PC-Deep Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>2764.8</v>
+      </c>
+      <c r="E80" t="n">
+        <v>426</v>
+      </c>
+      <c r="F80" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>PC-Gentle 4oz</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>2749.25</v>
+      </c>
+      <c r="E81" t="n">
+        <v>423.6</v>
+      </c>
+      <c r="F81" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>PC-Total 6oz</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>2743.76</v>
+      </c>
+      <c r="E82" t="n">
+        <v>422.8</v>
+      </c>
+      <c r="F82" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>CP-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>2917.4</v>
+      </c>
+      <c r="E83" t="n">
+        <v>680</v>
+      </c>
+      <c r="F83" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>CP-Cavity Shield 4oz</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>2846.35</v>
+      </c>
+      <c r="E84" t="n">
+        <v>663.5</v>
+      </c>
+      <c r="F84" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>CP-Mint Blast 6oz</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>2843.45</v>
+      </c>
+      <c r="E85" t="n">
+        <v>662.8</v>
+      </c>
+      <c r="F85" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>DS-Original 6oz</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>2663.66</v>
+      </c>
+      <c r="E86" t="n">
+        <v>651.3</v>
+      </c>
+      <c r="F86" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>DS-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>2594.09</v>
+      </c>
+      <c r="E87" t="n">
+        <v>634.3</v>
+      </c>
+      <c r="F87" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>DS-Cool Mint 6oz</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>2695.1</v>
+      </c>
+      <c r="E88" t="n">
+        <v>658.9</v>
+      </c>
+      <c r="F88" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>SC-Basic Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>2252.04</v>
+      </c>
+      <c r="E89" t="n">
+        <v>807.2</v>
+      </c>
+      <c r="F89" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>SC-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>2149</v>
+      </c>
+      <c r="E90" t="n">
+        <v>770.3</v>
+      </c>
+      <c r="F90" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>SC-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>2170.85</v>
+      </c>
+      <c r="E91" t="n">
+        <v>778.1</v>
+      </c>
+      <c r="F91" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>5413.53</v>
+      </c>
+      <c r="E92" t="n">
+        <v>1074.1</v>
+      </c>
+      <c r="F92" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="G92" t="n">
+        <v>1342.64</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>5755</v>
+      </c>
+      <c r="E93" t="n">
+        <v>1141.9</v>
+      </c>
+      <c r="F93" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="G93" t="n">
+        <v>1427.33</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>5419.24</v>
+      </c>
+      <c r="E94" t="n">
+        <v>1075.2</v>
+      </c>
+      <c r="F94" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="G94" t="n">
+        <v>1344.06</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>PC-Deep Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>2777.97</v>
+      </c>
+      <c r="E95" t="n">
+        <v>428</v>
+      </c>
+      <c r="F95" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>PC-Gentle 4oz</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>2871.29</v>
+      </c>
+      <c r="E96" t="n">
+        <v>442.4</v>
+      </c>
+      <c r="F96" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>PC-Total 6oz</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>2880.39</v>
+      </c>
+      <c r="E97" t="n">
+        <v>443.8</v>
+      </c>
+      <c r="F97" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>CP-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>2880.87</v>
+      </c>
+      <c r="E98" t="n">
+        <v>671.5</v>
+      </c>
+      <c r="F98" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>CP-Cavity Shield 4oz</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>2836.79</v>
+      </c>
+      <c r="E99" t="n">
+        <v>661.3</v>
+      </c>
+      <c r="F99" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>CP-Mint Blast 6oz</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>2861.39</v>
+      </c>
+      <c r="E100" t="n">
+        <v>667</v>
+      </c>
+      <c r="F100" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>DS-Original 6oz</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>2514.32</v>
+      </c>
+      <c r="E101" t="n">
+        <v>614.7</v>
+      </c>
+      <c r="F101" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>DS-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>2541.79</v>
+      </c>
+      <c r="E102" t="n">
+        <v>621.5</v>
+      </c>
+      <c r="F102" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>DS-Cool Mint 6oz</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>2619.62</v>
+      </c>
+      <c r="E103" t="n">
+        <v>640.5</v>
+      </c>
+      <c r="F103" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>SC-Basic Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>2305.65</v>
+      </c>
+      <c r="E104" t="n">
+        <v>826.4</v>
+      </c>
+      <c r="F104" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>SC-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>2238.65</v>
+      </c>
+      <c r="E105" t="n">
+        <v>802.4</v>
+      </c>
+      <c r="F105" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>SC-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>2254.5</v>
+      </c>
+      <c r="E106" t="n">
+        <v>808.1</v>
+      </c>
+      <c r="F106" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>5411.77</v>
+      </c>
+      <c r="E107" t="n">
+        <v>1073.8</v>
+      </c>
+      <c r="F107" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="G107" t="n">
+        <v>1342.21</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>5677.31</v>
+      </c>
+      <c r="E108" t="n">
+        <v>1126.5</v>
+      </c>
+      <c r="F108" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="G108" t="n">
+        <v>1408.06</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>5596.24</v>
+      </c>
+      <c r="E109" t="n">
+        <v>1110.4</v>
+      </c>
+      <c r="F109" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="G109" t="n">
+        <v>1387.96</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>PC-Deep Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>2855.3</v>
+      </c>
+      <c r="E110" t="n">
+        <v>440</v>
+      </c>
+      <c r="F110" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>PC-Gentle 4oz</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>2874.1</v>
+      </c>
+      <c r="E111" t="n">
+        <v>442.9</v>
+      </c>
+      <c r="F111" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>PC-Total 6oz</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>2740.72</v>
+      </c>
+      <c r="E112" t="n">
+        <v>422.3</v>
+      </c>
+      <c r="F112" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>CP-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>2846.55</v>
+      </c>
+      <c r="E113" t="n">
+        <v>663.5</v>
+      </c>
+      <c r="F113" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>CP-Cavity Shield 4oz</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>2878.41</v>
+      </c>
+      <c r="E114" t="n">
+        <v>671</v>
+      </c>
+      <c r="F114" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>CP-Mint Blast 6oz</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>2928.31</v>
+      </c>
+      <c r="E115" t="n">
+        <v>682.6</v>
+      </c>
+      <c r="F115" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>DS-Original 6oz</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>2698.22</v>
+      </c>
+      <c r="E116" t="n">
+        <v>659.7</v>
+      </c>
+      <c r="F116" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>DS-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>2579.97</v>
+      </c>
+      <c r="E117" t="n">
+        <v>630.8</v>
+      </c>
+      <c r="F117" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>DS-Cool Mint 6oz</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>2661.77</v>
+      </c>
+      <c r="E118" t="n">
+        <v>650.8</v>
+      </c>
+      <c r="F118" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>SC-Basic Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>2239.23</v>
+      </c>
+      <c r="E119" t="n">
+        <v>802.6</v>
+      </c>
+      <c r="F119" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>SC-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>2175.36</v>
+      </c>
+      <c r="E120" t="n">
+        <v>779.7</v>
+      </c>
+      <c r="F120" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>SC-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>2199.99</v>
+      </c>
+      <c r="E121" t="n">
+        <v>788.5</v>
+      </c>
+      <c r="F121" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>2451.33</v>
+      </c>
+      <c r="E122" t="n">
+        <v>389.7</v>
+      </c>
+      <c r="F122" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>2455.14</v>
+      </c>
+      <c r="E123" t="n">
+        <v>390.3</v>
+      </c>
+      <c r="F123" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>2409.01</v>
+      </c>
+      <c r="E124" t="n">
+        <v>383</v>
+      </c>
+      <c r="F124" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>PC-Deep Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>2857.1</v>
+      </c>
+      <c r="E125" t="n">
+        <v>440.2</v>
+      </c>
+      <c r="F125" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>PC-Gentle 4oz</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>2972.35</v>
+      </c>
+      <c r="E126" t="n">
+        <v>458</v>
+      </c>
+      <c r="F126" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>PC-Total 6oz</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>2843.14</v>
+      </c>
+      <c r="E127" t="n">
+        <v>438.1</v>
+      </c>
+      <c r="F127" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>CP-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>3107.91</v>
+      </c>
+      <c r="E128" t="n">
+        <v>724.5</v>
+      </c>
+      <c r="F128" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>CP-Cavity Shield 4oz</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>2928.02</v>
+      </c>
+      <c r="E129" t="n">
+        <v>682.5</v>
+      </c>
+      <c r="F129" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>CP-Mint Blast 6oz</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>2908.66</v>
+      </c>
+      <c r="E130" t="n">
+        <v>678</v>
+      </c>
+      <c r="F130" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>DS-Original 6oz</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>2658</v>
+      </c>
+      <c r="E131" t="n">
+        <v>649.9</v>
+      </c>
+      <c r="F131" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>DS-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>2662.66</v>
+      </c>
+      <c r="E132" t="n">
+        <v>651</v>
+      </c>
+      <c r="F132" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>DS-Cool Mint 6oz</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>2660.24</v>
+      </c>
+      <c r="E133" t="n">
+        <v>650.4</v>
+      </c>
+      <c r="F133" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>SC-Basic Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>2220.69</v>
+      </c>
+      <c r="E134" t="n">
+        <v>795.9</v>
+      </c>
+      <c r="F134" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>SC-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>2320.35</v>
+      </c>
+      <c r="E135" t="n">
+        <v>831.7</v>
+      </c>
+      <c r="F135" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>SC-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>2229.55</v>
+      </c>
+      <c r="E136" t="n">
+        <v>799.1</v>
+      </c>
+      <c r="F136" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>2511.56</v>
+      </c>
+      <c r="E137" t="n">
+        <v>399.3</v>
+      </c>
+      <c r="F137" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>2500.25</v>
+      </c>
+      <c r="E138" t="n">
+        <v>397.5</v>
+      </c>
+      <c r="F138" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>2428.81</v>
+      </c>
+      <c r="E139" t="n">
+        <v>386.1</v>
+      </c>
+      <c r="F139" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>PC-Deep Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>2942.22</v>
+      </c>
+      <c r="E140" t="n">
+        <v>453.3</v>
+      </c>
+      <c r="F140" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>PC-Gentle 4oz</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>2856.94</v>
+      </c>
+      <c r="E141" t="n">
+        <v>440.2</v>
+      </c>
+      <c r="F141" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>PC-Total 6oz</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>2952.65</v>
+      </c>
+      <c r="E142" t="n">
+        <v>455</v>
+      </c>
+      <c r="F142" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>CP-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>2895.09</v>
+      </c>
+      <c r="E143" t="n">
+        <v>674.8</v>
+      </c>
+      <c r="F143" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>CP-Cavity Shield 4oz</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>3118.65</v>
+      </c>
+      <c r="E144" t="n">
+        <v>727</v>
+      </c>
+      <c r="F144" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G144" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>CP-Mint Blast 6oz</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>2995.55</v>
+      </c>
+      <c r="E145" t="n">
+        <v>698.3</v>
+      </c>
+      <c r="F145" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>DS-Original 6oz</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>2742.88</v>
+      </c>
+      <c r="E146" t="n">
+        <v>670.6</v>
+      </c>
+      <c r="F146" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G146" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>DS-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>2653.3</v>
+      </c>
+      <c r="E147" t="n">
+        <v>648.7</v>
+      </c>
+      <c r="F147" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G147" t="n">
+        <v>0</v>
+      </c>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>DS-Cool Mint 6oz</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>2564.99</v>
+      </c>
+      <c r="E148" t="n">
+        <v>627.1</v>
+      </c>
+      <c r="F148" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G148" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>SC-Basic Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>2289.53</v>
+      </c>
+      <c r="E149" t="n">
+        <v>820.6</v>
+      </c>
+      <c r="F149" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G149" t="n">
+        <v>0</v>
+      </c>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>SC-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>2258.46</v>
+      </c>
+      <c r="E150" t="n">
+        <v>809.5</v>
+      </c>
+      <c r="F150" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G150" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>SC-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>2282.31</v>
+      </c>
+      <c r="E151" t="n">
+        <v>818</v>
+      </c>
+      <c r="F151" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0</v>
+      </c>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>2626.62</v>
+      </c>
+      <c r="E152" t="n">
+        <v>417.6</v>
+      </c>
+      <c r="F152" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G152" t="n">
+        <v>0</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I152" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J152" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>2670.95</v>
+      </c>
+      <c r="E153" t="n">
+        <v>424.6</v>
+      </c>
+      <c r="F153" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I153" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J153" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>2717.09</v>
+      </c>
+      <c r="E154" t="n">
+        <v>432</v>
+      </c>
+      <c r="F154" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G154" t="n">
+        <v>0</v>
+      </c>
+      <c r="H154" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I154" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J154" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>PC-Deep Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>2951.12</v>
+      </c>
+      <c r="E155" t="n">
+        <v>454.7</v>
+      </c>
+      <c r="F155" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G155" t="n">
+        <v>0</v>
+      </c>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>PC-Gentle 4oz</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>2884.91</v>
+      </c>
+      <c r="E156" t="n">
+        <v>444.5</v>
+      </c>
+      <c r="F156" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G156" t="n">
+        <v>0</v>
+      </c>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>PC-Total 6oz</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>2958.47</v>
+      </c>
+      <c r="E157" t="n">
+        <v>455.9</v>
+      </c>
+      <c r="F157" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G157" t="n">
+        <v>0</v>
+      </c>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>CP-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>3044.29</v>
+      </c>
+      <c r="E158" t="n">
+        <v>709.6</v>
+      </c>
+      <c r="F158" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G158" t="n">
+        <v>0</v>
+      </c>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>CP-Cavity Shield 4oz</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>3113.65</v>
+      </c>
+      <c r="E159" t="n">
+        <v>725.8</v>
+      </c>
+      <c r="F159" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G159" t="n">
+        <v>0</v>
+      </c>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>CP-Mint Blast 6oz</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>2971.99</v>
+      </c>
+      <c r="E160" t="n">
+        <v>692.8</v>
+      </c>
+      <c r="F160" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G160" t="n">
+        <v>0</v>
+      </c>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>DS-Original 6oz</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>2642.57</v>
+      </c>
+      <c r="E161" t="n">
+        <v>646.1</v>
+      </c>
+      <c r="F161" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G161" t="n">
+        <v>0</v>
+      </c>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>DS-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>2724.88</v>
+      </c>
+      <c r="E162" t="n">
+        <v>666.2</v>
+      </c>
+      <c r="F162" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G162" t="n">
+        <v>0</v>
+      </c>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>DS-Cool Mint 6oz</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>2659.73</v>
+      </c>
+      <c r="E163" t="n">
+        <v>650.3</v>
+      </c>
+      <c r="F163" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G163" t="n">
+        <v>0</v>
+      </c>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>SC-Basic Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>2274.24</v>
+      </c>
+      <c r="E164" t="n">
+        <v>815.1</v>
+      </c>
+      <c r="F164" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G164" t="n">
+        <v>0</v>
+      </c>
+      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>SC-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>2224.81</v>
+      </c>
+      <c r="E165" t="n">
+        <v>797.4</v>
+      </c>
+      <c r="F165" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G165" t="n">
+        <v>0</v>
+      </c>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>SC-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>2181.2</v>
+      </c>
+      <c r="E166" t="n">
+        <v>781.8</v>
+      </c>
+      <c r="F166" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G166" t="n">
+        <v>0</v>
+      </c>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>2789.82</v>
+      </c>
+      <c r="E167" t="n">
+        <v>443.5</v>
+      </c>
+      <c r="F167" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G167" t="n">
+        <v>0</v>
+      </c>
+      <c r="H167" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I167" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J167" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>2655.41</v>
+      </c>
+      <c r="E168" t="n">
+        <v>422.2</v>
+      </c>
+      <c r="F168" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G168" t="n">
+        <v>0</v>
+      </c>
+      <c r="H168" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I168" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J168" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>2670.17</v>
+      </c>
+      <c r="E169" t="n">
+        <v>424.5</v>
+      </c>
+      <c r="F169" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G169" t="n">
+        <v>0</v>
+      </c>
+      <c r="H169" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I169" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J169" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>PC-Deep Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>2950.13</v>
+      </c>
+      <c r="E170" t="n">
+        <v>454.6</v>
+      </c>
+      <c r="F170" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G170" t="n">
+        <v>0</v>
+      </c>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>PC-Gentle 4oz</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>2978.27</v>
+      </c>
+      <c r="E171" t="n">
+        <v>458.9</v>
+      </c>
+      <c r="F171" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G171" t="n">
+        <v>0</v>
+      </c>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>PC-Total 6oz</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>3012.71</v>
+      </c>
+      <c r="E172" t="n">
+        <v>464.2</v>
+      </c>
+      <c r="F172" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G172" t="n">
+        <v>0</v>
+      </c>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>CP-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>2948.37</v>
+      </c>
+      <c r="E173" t="n">
+        <v>687.3</v>
+      </c>
+      <c r="F173" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G173" t="n">
+        <v>0</v>
+      </c>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>CP-Cavity Shield 4oz</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>2909.48</v>
+      </c>
+      <c r="E174" t="n">
+        <v>678.2</v>
+      </c>
+      <c r="F174" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G174" t="n">
+        <v>0</v>
+      </c>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>CP-Mint Blast 6oz</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>3112.56</v>
+      </c>
+      <c r="E175" t="n">
+        <v>725.5</v>
+      </c>
+      <c r="F175" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G175" t="n">
+        <v>0</v>
+      </c>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>DS-Original 6oz</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>2585</v>
+      </c>
+      <c r="E176" t="n">
+        <v>632</v>
+      </c>
+      <c r="F176" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G176" t="n">
+        <v>0</v>
+      </c>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>DS-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>2594.2</v>
+      </c>
+      <c r="E177" t="n">
+        <v>634.3</v>
+      </c>
+      <c r="F177" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G177" t="n">
+        <v>0</v>
+      </c>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>DS-Cool Mint 6oz</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>2614.12</v>
+      </c>
+      <c r="E178" t="n">
+        <v>639.1</v>
+      </c>
+      <c r="F178" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G178" t="n">
+        <v>0</v>
+      </c>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>SC-Basic Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>2237.25</v>
+      </c>
+      <c r="E179" t="n">
+        <v>801.9</v>
+      </c>
+      <c r="F179" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G179" t="n">
+        <v>0</v>
+      </c>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>SC-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>2300.36</v>
+      </c>
+      <c r="E180" t="n">
+        <v>824.5</v>
+      </c>
+      <c r="F180" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G180" t="n">
+        <v>0</v>
+      </c>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>SC-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>2278.52</v>
+      </c>
+      <c r="E181" t="n">
+        <v>816.7</v>
+      </c>
+      <c r="F181" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G181" t="n">
+        <v>0</v>
+      </c>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>2877.64</v>
+      </c>
+      <c r="E182" t="n">
+        <v>457.5</v>
+      </c>
+      <c r="F182" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G182" t="n">
+        <v>0</v>
+      </c>
+      <c r="H182" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I182" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J182" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>2756.95</v>
+      </c>
+      <c r="E183" t="n">
+        <v>438.3</v>
+      </c>
+      <c r="F183" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G183" t="n">
+        <v>0</v>
+      </c>
+      <c r="H183" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I183" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J183" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>2798.27</v>
+      </c>
+      <c r="E184" t="n">
+        <v>444.9</v>
+      </c>
+      <c r="F184" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G184" t="n">
+        <v>0</v>
+      </c>
+      <c r="H184" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I184" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J184" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>PC-Deep Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>2915.45</v>
+      </c>
+      <c r="E185" t="n">
+        <v>449.2</v>
+      </c>
+      <c r="F185" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G185" t="n">
+        <v>0</v>
+      </c>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>PC-Gentle 4oz</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>2838.12</v>
+      </c>
+      <c r="E186" t="n">
+        <v>437.3</v>
+      </c>
+      <c r="F186" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G186" t="n">
+        <v>0</v>
+      </c>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>PC-Total 6oz</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>2867.56</v>
+      </c>
+      <c r="E187" t="n">
+        <v>441.8</v>
+      </c>
+      <c r="F187" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G187" t="n">
+        <v>0</v>
+      </c>
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>CP-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>2956.95</v>
+      </c>
+      <c r="E188" t="n">
+        <v>689.3</v>
+      </c>
+      <c r="F188" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G188" t="n">
+        <v>0</v>
+      </c>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>CP-Cavity Shield 4oz</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>2913.46</v>
+      </c>
+      <c r="E189" t="n">
+        <v>679.1</v>
+      </c>
+      <c r="F189" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G189" t="n">
+        <v>0</v>
+      </c>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>CP-Mint Blast 6oz</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>3015.07</v>
+      </c>
+      <c r="E190" t="n">
+        <v>702.8</v>
+      </c>
+      <c r="F190" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G190" t="n">
+        <v>0</v>
+      </c>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>DS-Original 6oz</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>2702.11</v>
+      </c>
+      <c r="E191" t="n">
+        <v>660.7</v>
+      </c>
+      <c r="F191" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G191" t="n">
+        <v>0</v>
+      </c>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>DS-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>2567.03</v>
+      </c>
+      <c r="E192" t="n">
+        <v>627.6</v>
+      </c>
+      <c r="F192" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G192" t="n">
+        <v>0</v>
+      </c>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr"/>
+      <c r="J192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>DS-Cool Mint 6oz</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>2654.49</v>
+      </c>
+      <c r="E193" t="n">
+        <v>649</v>
+      </c>
+      <c r="F193" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G193" t="n">
+        <v>0</v>
+      </c>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr"/>
+      <c r="J193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>SC-Basic Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>2282.39</v>
+      </c>
+      <c r="E194" t="n">
+        <v>818.1</v>
+      </c>
+      <c r="F194" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G194" t="n">
+        <v>0</v>
+      </c>
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr"/>
+      <c r="J194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>SC-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>2276.28</v>
+      </c>
+      <c r="E195" t="n">
+        <v>815.9</v>
+      </c>
+      <c r="F195" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G195" t="n">
+        <v>0</v>
+      </c>
+      <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>SC-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>2288.26</v>
+      </c>
+      <c r="E196" t="n">
+        <v>820.2</v>
+      </c>
+      <c r="F196" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G196" t="n">
+        <v>0</v>
+      </c>
+      <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
+      <c r="J196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>2912.74</v>
+      </c>
+      <c r="E197" t="n">
+        <v>463.1</v>
+      </c>
+      <c r="F197" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G197" t="n">
+        <v>0</v>
+      </c>
+      <c r="H197" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I197" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J197" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>2999.86</v>
+      </c>
+      <c r="E198" t="n">
+        <v>476.9</v>
+      </c>
+      <c r="F198" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G198" t="n">
+        <v>0</v>
+      </c>
+      <c r="H198" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I198" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J198" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>2864.19</v>
+      </c>
+      <c r="E199" t="n">
+        <v>455.4</v>
+      </c>
+      <c r="F199" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G199" t="n">
+        <v>0</v>
+      </c>
+      <c r="H199" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I199" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J199" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>PC-Deep Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>2887.98</v>
+      </c>
+      <c r="E200" t="n">
+        <v>445</v>
+      </c>
+      <c r="F200" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G200" t="n">
+        <v>0</v>
+      </c>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr"/>
+      <c r="J200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>PC-Gentle 4oz</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>2844.88</v>
+      </c>
+      <c r="E201" t="n">
+        <v>438.3</v>
+      </c>
+      <c r="F201" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G201" t="n">
+        <v>0</v>
+      </c>
+      <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr"/>
+      <c r="J201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>PC-Total 6oz</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>2912.9</v>
+      </c>
+      <c r="E202" t="n">
+        <v>448.8</v>
+      </c>
+      <c r="F202" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G202" t="n">
+        <v>0</v>
+      </c>
+      <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr"/>
+      <c r="J202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>CP-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>2977.07</v>
+      </c>
+      <c r="E203" t="n">
+        <v>694</v>
+      </c>
+      <c r="F203" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G203" t="n">
+        <v>0</v>
+      </c>
+      <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr"/>
+      <c r="J203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>CP-Cavity Shield 4oz</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>2940.76</v>
+      </c>
+      <c r="E204" t="n">
+        <v>685.5</v>
+      </c>
+      <c r="F204" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G204" t="n">
+        <v>0</v>
+      </c>
+      <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr"/>
+      <c r="J204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>CP-Mint Blast 6oz</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>3063.49</v>
+      </c>
+      <c r="E205" t="n">
+        <v>714.1</v>
+      </c>
+      <c r="F205" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G205" t="n">
+        <v>0</v>
+      </c>
+      <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr"/>
+      <c r="J205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>DS-Original 6oz</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>2618.91</v>
+      </c>
+      <c r="E206" t="n">
+        <v>640.3</v>
+      </c>
+      <c r="F206" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G206" t="n">
+        <v>0</v>
+      </c>
+      <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr"/>
+      <c r="J206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>DS-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>2610.18</v>
+      </c>
+      <c r="E207" t="n">
+        <v>638.2</v>
+      </c>
+      <c r="F207" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G207" t="n">
+        <v>0</v>
+      </c>
+      <c r="H207" t="inlineStr"/>
+      <c r="I207" t="inlineStr"/>
+      <c r="J207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>DS-Cool Mint 6oz</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>2580</v>
+      </c>
+      <c r="E208" t="n">
+        <v>630.8</v>
+      </c>
+      <c r="F208" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G208" t="n">
+        <v>0</v>
+      </c>
+      <c r="H208" t="inlineStr"/>
+      <c r="I208" t="inlineStr"/>
+      <c r="J208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>SC-Basic Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>2221.08</v>
+      </c>
+      <c r="E209" t="n">
+        <v>796.1</v>
+      </c>
+      <c r="F209" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G209" t="n">
+        <v>0</v>
+      </c>
+      <c r="H209" t="inlineStr"/>
+      <c r="I209" t="inlineStr"/>
+      <c r="J209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>SC-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>2196.82</v>
+      </c>
+      <c r="E210" t="n">
+        <v>787.4</v>
+      </c>
+      <c r="F210" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G210" t="n">
+        <v>0</v>
+      </c>
+      <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr"/>
+      <c r="J210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>SC-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>2208.66</v>
+      </c>
+      <c r="E211" t="n">
+        <v>791.6</v>
+      </c>
+      <c r="F211" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G211" t="n">
+        <v>0</v>
+      </c>
+      <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr"/>
+      <c r="J211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>2955.43</v>
+      </c>
+      <c r="E212" t="n">
+        <v>469.9</v>
+      </c>
+      <c r="F212" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G212" t="n">
+        <v>0</v>
+      </c>
+      <c r="H212" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I212" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J212" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>3082.76</v>
+      </c>
+      <c r="E213" t="n">
+        <v>490.1</v>
+      </c>
+      <c r="F213" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G213" t="n">
+        <v>0</v>
+      </c>
+      <c r="H213" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I213" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J213" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>3123.06</v>
+      </c>
+      <c r="E214" t="n">
+        <v>496.5</v>
+      </c>
+      <c r="F214" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G214" t="n">
+        <v>0</v>
+      </c>
+      <c r="H214" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I214" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J214" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>PC-Deep Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>2920.02</v>
+      </c>
+      <c r="E215" t="n">
+        <v>449.9</v>
+      </c>
+      <c r="F215" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G215" t="n">
+        <v>0</v>
+      </c>
+      <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr"/>
+      <c r="J215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>PC-Gentle 4oz</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>2953.91</v>
+      </c>
+      <c r="E216" t="n">
+        <v>455.1</v>
+      </c>
+      <c r="F216" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G216" t="n">
+        <v>0</v>
+      </c>
+      <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr"/>
+      <c r="J216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>PC-Total 6oz</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>3006.29</v>
+      </c>
+      <c r="E217" t="n">
+        <v>463.2</v>
+      </c>
+      <c r="F217" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G217" t="n">
+        <v>0</v>
+      </c>
+      <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr"/>
+      <c r="J217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>CP-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>3122.84</v>
+      </c>
+      <c r="E218" t="n">
+        <v>727.9</v>
+      </c>
+      <c r="F218" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G218" t="n">
+        <v>0</v>
+      </c>
+      <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr"/>
+      <c r="J218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>CP-Cavity Shield 4oz</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>3030.27</v>
+      </c>
+      <c r="E219" t="n">
+        <v>706.4</v>
+      </c>
+      <c r="F219" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G219" t="n">
+        <v>0</v>
+      </c>
+      <c r="H219" t="inlineStr"/>
+      <c r="I219" t="inlineStr"/>
+      <c r="J219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>CP-Mint Blast 6oz</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>3096.64</v>
+      </c>
+      <c r="E220" t="n">
+        <v>721.8</v>
+      </c>
+      <c r="F220" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G220" t="n">
+        <v>0</v>
+      </c>
+      <c r="H220" t="inlineStr"/>
+      <c r="I220" t="inlineStr"/>
+      <c r="J220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>DS-Original 6oz</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>2745.4</v>
+      </c>
+      <c r="E221" t="n">
+        <v>671.2</v>
+      </c>
+      <c r="F221" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G221" t="n">
+        <v>0</v>
+      </c>
+      <c r="H221" t="inlineStr"/>
+      <c r="I221" t="inlineStr"/>
+      <c r="J221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>DS-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>2720.49</v>
+      </c>
+      <c r="E222" t="n">
+        <v>665.2</v>
+      </c>
+      <c r="F222" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G222" t="n">
+        <v>0</v>
+      </c>
+      <c r="H222" t="inlineStr"/>
+      <c r="I222" t="inlineStr"/>
+      <c r="J222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>DS-Cool Mint 6oz</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>2650.19</v>
+      </c>
+      <c r="E223" t="n">
+        <v>648</v>
+      </c>
+      <c r="F223" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G223" t="n">
+        <v>0</v>
+      </c>
+      <c r="H223" t="inlineStr"/>
+      <c r="I223" t="inlineStr"/>
+      <c r="J223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>SC-Basic Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>2157.21</v>
+      </c>
+      <c r="E224" t="n">
+        <v>773.2</v>
+      </c>
+      <c r="F224" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G224" t="n">
+        <v>0</v>
+      </c>
+      <c r="H224" t="inlineStr"/>
+      <c r="I224" t="inlineStr"/>
+      <c r="J224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>SC-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>2145.54</v>
+      </c>
+      <c r="E225" t="n">
+        <v>769</v>
+      </c>
+      <c r="F225" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G225" t="n">
+        <v>0</v>
+      </c>
+      <c r="H225" t="inlineStr"/>
+      <c r="I225" t="inlineStr"/>
+      <c r="J225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>SC-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>2227.93</v>
+      </c>
+      <c r="E226" t="n">
+        <v>798.5</v>
+      </c>
+      <c r="F226" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G226" t="n">
+        <v>0</v>
+      </c>
+      <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr"/>
+      <c r="J226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>3143.57</v>
+      </c>
+      <c r="E227" t="n">
+        <v>499.8</v>
+      </c>
+      <c r="F227" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G227" t="n">
+        <v>0</v>
+      </c>
+      <c r="H227" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I227" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J227" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>3121.69</v>
+      </c>
+      <c r="E228" t="n">
+        <v>496.3</v>
+      </c>
+      <c r="F228" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G228" t="n">
+        <v>0</v>
+      </c>
+      <c r="H228" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I228" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J228" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>3162.15</v>
+      </c>
+      <c r="E229" t="n">
+        <v>502.7</v>
+      </c>
+      <c r="F229" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="G229" t="n">
+        <v>0</v>
+      </c>
+      <c r="H229" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I229" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J229" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>PC-Deep Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>2932.69</v>
+      </c>
+      <c r="E230" t="n">
+        <v>451.9</v>
+      </c>
+      <c r="F230" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G230" t="n">
+        <v>0</v>
+      </c>
+      <c r="H230" t="inlineStr"/>
+      <c r="I230" t="inlineStr"/>
+      <c r="J230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>PC-Gentle 4oz</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>2999.15</v>
+      </c>
+      <c r="E231" t="n">
+        <v>462.1</v>
+      </c>
+      <c r="F231" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G231" t="n">
+        <v>0</v>
+      </c>
+      <c r="H231" t="inlineStr"/>
+      <c r="I231" t="inlineStr"/>
+      <c r="J231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>PearlCare</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>PC-Total 6oz</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>2829.07</v>
+      </c>
+      <c r="E232" t="n">
+        <v>435.9</v>
+      </c>
+      <c r="F232" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G232" t="n">
+        <v>0</v>
+      </c>
+      <c r="H232" t="inlineStr"/>
+      <c r="I232" t="inlineStr"/>
+      <c r="J232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>CP-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>2936.98</v>
+      </c>
+      <c r="E233" t="n">
+        <v>684.6</v>
+      </c>
+      <c r="F233" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G233" t="n">
+        <v>0</v>
+      </c>
+      <c r="H233" t="inlineStr"/>
+      <c r="I233" t="inlineStr"/>
+      <c r="J233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>CP-Cavity Shield 4oz</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>3073.39</v>
+      </c>
+      <c r="E234" t="n">
+        <v>716.4</v>
+      </c>
+      <c r="F234" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G234" t="n">
+        <v>0</v>
+      </c>
+      <c r="H234" t="inlineStr"/>
+      <c r="I234" t="inlineStr"/>
+      <c r="J234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>CleanPro</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>CP-Mint Blast 6oz</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>3086.56</v>
+      </c>
+      <c r="E235" t="n">
+        <v>719.5</v>
+      </c>
+      <c r="F235" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G235" t="n">
+        <v>0</v>
+      </c>
+      <c r="H235" t="inlineStr"/>
+      <c r="I235" t="inlineStr"/>
+      <c r="J235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>DS-Original 6oz</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>2763.74</v>
+      </c>
+      <c r="E236" t="n">
+        <v>675.7</v>
+      </c>
+      <c r="F236" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G236" t="n">
+        <v>0</v>
+      </c>
+      <c r="H236" t="inlineStr"/>
+      <c r="I236" t="inlineStr"/>
+      <c r="J236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>DS-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>2737.81</v>
+      </c>
+      <c r="E237" t="n">
+        <v>669.4</v>
+      </c>
+      <c r="F237" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G237" t="n">
+        <v>0</v>
+      </c>
+      <c r="H237" t="inlineStr"/>
+      <c r="I237" t="inlineStr"/>
+      <c r="J237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>DailyShine</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>DS-Cool Mint 6oz</t>
+        </is>
+      </c>
+      <c r="D238" t="n">
+        <v>2741.42</v>
+      </c>
+      <c r="E238" t="n">
+        <v>670.3</v>
+      </c>
+      <c r="F238" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G238" t="n">
+        <v>0</v>
+      </c>
+      <c r="H238" t="inlineStr"/>
+      <c r="I238" t="inlineStr"/>
+      <c r="J238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>SC-Basic Clean 6oz</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
+        <v>2198.85</v>
+      </c>
+      <c r="E239" t="n">
+        <v>788.1</v>
+      </c>
+      <c r="F239" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G239" t="n">
+        <v>0</v>
+      </c>
+      <c r="H239" t="inlineStr"/>
+      <c r="I239" t="inlineStr"/>
+      <c r="J239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>SC-Whitening 4oz</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>2214.44</v>
+      </c>
+      <c r="E240" t="n">
+        <v>793.7</v>
+      </c>
+      <c r="F240" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G240" t="n">
+        <v>0</v>
+      </c>
+      <c r="H240" t="inlineStr"/>
+      <c r="I240" t="inlineStr"/>
+      <c r="J240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>SmartChoice</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>SC-Fresh 6oz</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>2190.59</v>
+      </c>
+      <c r="E241" t="n">
+        <v>785.2</v>
+      </c>
+      <c r="F241" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G241" t="n">
+        <v>0</v>
+      </c>
+      <c r="H241" t="inlineStr"/>
+      <c r="I241" t="inlineStr"/>
+      <c r="J241" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
